--- a/public/templates/bulk_question_template.xlsx
+++ b/public/templates/bulk_question_template.xlsx
@@ -406,8 +406,8 @@
       <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2">
-        <v>5.0</v>
+      <c r="D2" s="3">
+        <v>1.0</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
@@ -432,8 +432,8 @@
       <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2">
-        <v>10.0</v>
+      <c r="D3" s="3">
+        <v>1.0</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>17</v>
